--- a/publication_tables/main/table4.xlsx
+++ b/publication_tables/main/table4.xlsx
@@ -484,7 +484,7 @@
         <v>-0.122</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.108</v>
+        <v>-0.107</v>
       </c>
     </row>
   </sheetData>
@@ -498,90 +498,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Table 4. Recipient composition contributions to the PMT poverty-gap advantage</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Note. Negative differences indicate a lower FGT1 under PMT or group-matched allocation at the corresponding step. Ranges describe thirty paired recipient draws. pp: percentage points. Source: model simulations.</t>
+          <t>Contribution in the sequential matched-recipient decomposition. Values follow the displayed precision of Table 4. Recipient composition contributions to the PMT poverty-gap advantage. Full-precision simulation results accompany the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mean (pp)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mean FGT1 contribution across thirty paired draws, percentage points. Values follow the displayed precision of Table 4. Recipient composition contributions to the PMT poverty-gap advantage. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Minimum (pp)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Minimum FGT1 contribution across paired draws, percentage points. Values follow the displayed precision of Table 4. Recipient composition contributions to the PMT poverty-gap advantage. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Maximum (pp)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sequential contribution: between-quintile allocation, within-quintile selection, or their sum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mean (pp)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Average FGT1 contribution across thirty paired recipient draws (percentage points).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Minimum (pp)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Minimum contribution across the thirty paired draws (percentage points).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Maximum (pp)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Maximum contribution across the thirty paired draws (percentage points).</t>
+          <t>Maximum FGT1 contribution across paired draws, percentage points. Values follow the displayed precision of Table 4. Recipient composition contributions to the PMT poverty-gap advantage. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
